--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,48 +1016,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112209018</v>
+        <v>137359706</v>
       </c>
       <c r="B5" t="n">
-        <v>91923</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Risbäcken, Fjälliden, Ås lm</t>
+          <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539768</v>
+        <v>539724</v>
       </c>
       <c r="R5" t="n">
-        <v>7214451</v>
+        <v>7214464</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1101,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209018</t>
+          <t>https://artportalen.se/Sighting/137359706</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131935860</v>
+        <v>137359702</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>92732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539688</v>
+        <v>539724</v>
       </c>
       <c r="R6" t="n">
-        <v>7214436</v>
+        <v>7214464</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1203,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935860</t>
+          <t>https://artportalen.se/Sighting/137359702</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112209011</v>
+        <v>112209018</v>
       </c>
       <c r="B7" t="n">
-        <v>92292</v>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539775</v>
+        <v>539768</v>
       </c>
       <c r="R7" t="n">
-        <v>7214458</v>
+        <v>7214451</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1326,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209011</t>
+          <t>https://artportalen.se/Sighting/112209018</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112209029</v>
+        <v>131935860</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,34 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Risbäcken, Fjälliden, Ås lm</t>
+          <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539846</v>
+        <v>539688</v>
       </c>
       <c r="R8" t="n">
-        <v>7214346</v>
+        <v>7214436</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,22 +1397,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1432,22 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209029</t>
+          <t>https://artportalen.se/Sighting/131935860</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112209030</v>
+        <v>112209011</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>92292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539856</v>
+        <v>539775</v>
       </c>
       <c r="R9" t="n">
-        <v>7214398</v>
+        <v>7214458</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,13 +1550,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209030</t>
+          <t>https://artportalen.se/Sighting/112209011</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112209031</v>
+        <v>112209029</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1611,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539837</v>
+        <v>539846</v>
       </c>
       <c r="R10" t="n">
-        <v>7214404</v>
+        <v>7214346</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,13 +1662,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209031</t>
+          <t>https://artportalen.se/Sighting/112209029</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112209032</v>
+        <v>112209030</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1723,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539784</v>
+        <v>539856</v>
       </c>
       <c r="R11" t="n">
-        <v>7214443</v>
+        <v>7214398</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,13 +1774,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209032</t>
+          <t>https://artportalen.se/Sighting/112209030</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112209033</v>
+        <v>112209031</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1835,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539775</v>
+        <v>539837</v>
       </c>
       <c r="R12" t="n">
-        <v>7214457</v>
+        <v>7214404</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,13 +1886,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209033</t>
+          <t>https://artportalen.se/Sighting/112209031</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112209034</v>
+        <v>112209032</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1947,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539767</v>
+        <v>539784</v>
       </c>
       <c r="R13" t="n">
-        <v>7214452</v>
+        <v>7214443</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,13 +1998,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209034</t>
+          <t>https://artportalen.se/Sighting/112209032</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112209035</v>
+        <v>112209033</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2059,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539728</v>
+        <v>539775</v>
       </c>
       <c r="R14" t="n">
-        <v>7214469</v>
+        <v>7214457</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,13 +2110,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209035</t>
+          <t>https://artportalen.se/Sighting/112209033</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112209036</v>
+        <v>112209034</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2171,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539696</v>
+        <v>539767</v>
       </c>
       <c r="R15" t="n">
-        <v>7214436</v>
+        <v>7214452</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,13 +2222,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209036</t>
+          <t>https://artportalen.se/Sighting/112209034</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130175807</v>
+        <v>112209035</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2279,14 +2259,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fjälliden, Ås lm</t>
+          <t>Risbäcken, Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539816</v>
+        <v>539728</v>
       </c>
       <c r="R16" t="n">
-        <v>7214462</v>
+        <v>7214469</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2313,22 +2293,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,19 +2328,19 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175807</t>
+          <t>https://artportalen.se/Sighting/112209035</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130175809</v>
+        <v>112209036</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2391,14 +2371,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fjälliden, Ås lm</t>
+          <t>Risbäcken, Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539893</v>
+        <v>539696</v>
       </c>
       <c r="R17" t="n">
-        <v>7214438</v>
+        <v>7214436</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2425,22 +2405,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,19 +2440,19 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175809</t>
+          <t>https://artportalen.se/Sighting/112209036</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130175811</v>
+        <v>130175807</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2507,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539929</v>
+        <v>539816</v>
       </c>
       <c r="R18" t="n">
-        <v>7214415</v>
+        <v>7214462</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,13 +2558,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175811</t>
+          <t>https://artportalen.se/Sighting/130175807</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130175813</v>
+        <v>130175809</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2619,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539967</v>
+        <v>539893</v>
       </c>
       <c r="R19" t="n">
-        <v>7214330</v>
+        <v>7214438</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,13 +2670,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175813</t>
+          <t>https://artportalen.se/Sighting/130175809</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130175814</v>
+        <v>130175811</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2731,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539988</v>
+        <v>539929</v>
       </c>
       <c r="R20" t="n">
-        <v>7214273</v>
+        <v>7214415</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,56 +2782,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175814</t>
+          <t>https://artportalen.se/Sighting/130175811</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112208992</v>
+        <v>130175813</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Risbäcken, Fjälliden, Ås lm</t>
+          <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539848</v>
+        <v>539967</v>
       </c>
       <c r="R21" t="n">
-        <v>7214344</v>
+        <v>7214330</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,22 +2853,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,62 +2888,57 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112208992</t>
+          <t>https://artportalen.se/Sighting/130175813</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112208993</v>
+        <v>130175814</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Risbäcken, Fjälliden, Ås lm</t>
+          <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539781</v>
+        <v>539988</v>
       </c>
       <c r="R22" t="n">
-        <v>7214440</v>
+        <v>7214273</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,22 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,19 +3000,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112208993</t>
+          <t>https://artportalen.se/Sighting/130175814</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112208994</v>
+        <v>112208992</v>
       </c>
       <c r="B23" t="n">
         <v>57953</v>
@@ -3082,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539730</v>
+        <v>539848</v>
       </c>
       <c r="R23" t="n">
-        <v>7214470</v>
+        <v>7214344</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +3087,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3097,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,13 +3123,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112208994</t>
+          <t>https://artportalen.se/Sighting/112208992</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112208995</v>
+        <v>112208993</v>
       </c>
       <c r="B24" t="n">
         <v>57953</v>
@@ -3190,7 +3160,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3199,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539697</v>
+        <v>539781</v>
       </c>
       <c r="R24" t="n">
-        <v>7214438</v>
+        <v>7214440</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,13 +3240,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112208995</t>
+          <t>https://artportalen.se/Sighting/112208993</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130175808</v>
+        <v>112208994</v>
       </c>
       <c r="B25" t="n">
         <v>57953</v>
@@ -3312,14 +3282,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fjälliden, Ås lm</t>
+          <t>Risbäcken, Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539816</v>
+        <v>539730</v>
       </c>
       <c r="R25" t="n">
-        <v>7214462</v>
+        <v>7214470</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3346,22 +3316,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,22 +3351,22 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175808</t>
+          <t>https://artportalen.se/Sighting/112208994</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130175812</v>
+        <v>112208995</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,43 +3374,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fjälliden, Ås lm</t>
+          <t>Risbäcken, Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539963</v>
+        <v>539697</v>
       </c>
       <c r="R26" t="n">
-        <v>7214332</v>
+        <v>7214438</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3467,22 +3433,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,22 +3468,22 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175812</t>
+          <t>https://artportalen.se/Sighting/112208995</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131935863</v>
+        <v>130175808</v>
       </c>
       <c r="B27" t="n">
-        <v>79452</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3525,34 +3491,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539698</v>
+        <v>539816</v>
       </c>
       <c r="R27" t="n">
-        <v>7214525</v>
+        <v>7214462</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3579,22 +3550,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,22 +3585,22 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935863</t>
+          <t>https://artportalen.se/Sighting/130175808</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131935887</v>
+        <v>130175812</v>
       </c>
       <c r="B28" t="n">
-        <v>79452</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3637,34 +3608,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539440</v>
+        <v>539963</v>
       </c>
       <c r="R28" t="n">
-        <v>7214622</v>
+        <v>7214332</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3691,22 +3671,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,44 +3706,44 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935887</t>
+          <t>https://artportalen.se/Sighting/130175812</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131935865</v>
+        <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>83222</v>
+        <v>78529</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3773,13 +3753,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539702</v>
+        <v>539679</v>
       </c>
       <c r="R29" t="n">
-        <v>7214521</v>
+        <v>7214501</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3803,22 +3783,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,49 +3803,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935865</t>
+          <t>https://artportalen.se/Sighting/137359710</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131935861</v>
+        <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>92167</v>
+        <v>78872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3885,13 +3855,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539702</v>
+        <v>539629</v>
       </c>
       <c r="R30" t="n">
-        <v>7214513</v>
+        <v>7214571</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3915,22 +3885,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,49 +3905,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935861</t>
+          <t>https://artportalen.se/Sighting/137359715</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130175797</v>
+        <v>131935863</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79452</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3997,10 +3957,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539541</v>
+        <v>539698</v>
       </c>
       <c r="R31" t="n">
-        <v>7214601</v>
+        <v>7214525</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4027,22 +3987,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,44 +4022,44 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175797</t>
+          <t>https://artportalen.se/Sighting/131935863</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130175806</v>
+        <v>131935887</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>79452</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4109,10 +4069,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539660</v>
+        <v>539440</v>
       </c>
       <c r="R32" t="n">
-        <v>7214545</v>
+        <v>7214622</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4139,22 +4099,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,44 +4134,44 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175806</t>
+          <t>https://artportalen.se/Sighting/131935887</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131935864</v>
+        <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4221,13 +4181,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>539699</v>
+        <v>539677</v>
       </c>
       <c r="R33" t="n">
-        <v>7214524</v>
+        <v>7214501</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4251,22 +4211,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,49 +4231,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935864</t>
+          <t>https://artportalen.se/Sighting/137359707</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131935886</v>
+        <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>92159</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4333,13 +4283,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539469</v>
+        <v>539597</v>
       </c>
       <c r="R34" t="n">
-        <v>7214614</v>
+        <v>7214568</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4363,22 +4313,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,49 +4333,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935886</t>
+          <t>https://artportalen.se/Sighting/137359704</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131935888</v>
+        <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>92591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4445,13 +4385,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539439</v>
+        <v>539597</v>
       </c>
       <c r="R35" t="n">
-        <v>7214622</v>
+        <v>7214567</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4475,22 +4415,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,27 +4435,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935888</t>
+          <t>https://artportalen.se/Sighting/137359712</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131935885</v>
+        <v>131935865</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>83222</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,39 +4463,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539467</v>
+        <v>539702</v>
       </c>
       <c r="R36" t="n">
-        <v>7214618</v>
+        <v>7214521</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4597,7 +4522,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4607,7 +4532,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4633,63 +4558,54 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131935885</t>
+          <t>https://artportalen.se/Sighting/131935865</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130175804</v>
+        <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>57791</v>
+        <v>83381</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102620</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539555</v>
+        <v>539678</v>
       </c>
       <c r="R37" t="n">
-        <v>7214788</v>
+        <v>7214501</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4713,22 +4629,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4743,27 +4649,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175804</t>
+          <t>https://artportalen.se/Sighting/137359698</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130175805</v>
+        <v>131935861</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>92167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,43 +4677,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>1588</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539575</v>
+        <v>539702</v>
       </c>
       <c r="R38" t="n">
-        <v>7214682</v>
+        <v>7214513</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4834,22 +4731,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4869,61 +4766,57 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130175805</t>
+          <t>https://artportalen.se/Sighting/131935861</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131935884</v>
+        <v>130175797</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539470</v>
+        <v>539541</v>
       </c>
       <c r="R39" t="n">
-        <v>7214625</v>
+        <v>7214601</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4950,22 +4843,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4985,11 +4878,1036 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Pär Eriksson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175797</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130175806</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>539660</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7214545</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175806</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131935864</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>539699</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7214524</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131935864</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131935886</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>539469</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7214614</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131935886</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131935888</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>539439</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7214622</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131935888</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137359700</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83502</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>539619</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7214578</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137359700</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131935885</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>539467</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7214618</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131935885</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130175804</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57791</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>539555</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7214788</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175804</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130175805</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>539575</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7214682</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175805</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131935884</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fjälliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>539470</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7214625</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131935884</t>
         </is>
@@ -5035,6 +5953,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112209006</v>
+        <v>137359702</v>
       </c>
       <c r="B4" t="n">
-        <v>92208</v>
+        <v>89523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +915,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Risbäcken, Fjälliden, Ås lm</t>
+          <t>Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539727</v>
+        <v>539724</v>
       </c>
       <c r="R4" t="n">
-        <v>7214473</v>
+        <v>7214464</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,33 +986,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112209006</t>
+          <t>https://artportalen.se/Sighting/137359702</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137359706</v>
+        <v>112209006</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,17 +1041,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjälliden, Ås lm</t>
+          <t>Risbäcken, Fjälliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539724</v>
+        <v>539727</v>
       </c>
       <c r="R5" t="n">
-        <v>7214464</v>
+        <v>7214473</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1075,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,49 +1105,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137359706</t>
+          <t>https://artportalen.se/Sighting/112209006</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137359702</v>
+        <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92732</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,7 +1218,7 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137359702</t>
+          <t>https://artportalen.se/Sighting/137359706</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3725,7 @@
         <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3827,7 @@
         <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>78872</v>
+        <v>78875</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4153,7 @@
         <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4251,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4567,7 +4571,7 @@
         <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5341,7 +5345,7 @@
         <v>137359700</v>
       </c>
       <c r="B44" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -1125,7 +1125,7 @@
         <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137359702</v>
       </c>
       <c r="B4" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>78875</v>
+        <v>78880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137359700</v>
       </c>
       <c r="B44" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137359702</v>
       </c>
       <c r="B4" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>78880</v>
+        <v>78891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137359700</v>
       </c>
       <c r="B44" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137359702</v>
       </c>
       <c r="B4" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>78891</v>
+        <v>78892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137359700</v>
       </c>
       <c r="B44" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137359702</v>
       </c>
       <c r="B4" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>78892</v>
+        <v>78894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137359700</v>
       </c>
       <c r="B44" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36619-2026 artfynd.xlsx
+++ b/artfynd/A 36619-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137359702</v>
       </c>
       <c r="B4" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137359706</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137359710</v>
       </c>
       <c r="B29" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>137359715</v>
       </c>
       <c r="B30" t="n">
-        <v>78894</v>
+        <v>78898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>137359707</v>
       </c>
       <c r="B33" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137359704</v>
       </c>
       <c r="B34" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>137359712</v>
       </c>
       <c r="B35" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137359698</v>
       </c>
       <c r="B37" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>137359700</v>
       </c>
       <c r="B44" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
